--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003491</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130333758</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>497053</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6587180</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130333947</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>497041</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6587251</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>130333758</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>130333947</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>130333758</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>130333947</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>130333758</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>130333947</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>130333758</v>
       </c>
       <c r="B3" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>130333947</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>130333758</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>130333947</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003491</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>130333758</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>130333947</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130003491</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>130333758</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>130333947</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130003491</v>
+        <v>130334062</v>
       </c>
       <c r="B2" t="n">
-        <v>57889</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Öknen norra torpet, Vikers sn, Vstm</t>
+          <t>Östra Öknen norra torpet, Östra Öknen norra torpet, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497049</v>
+        <v>497133</v>
       </c>
       <c r="R2" t="n">
-        <v>6587095</v>
+        <v>6587114</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hack i död björk</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,54 +767,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130333758</v>
+        <v>130003491</v>
       </c>
       <c r="B3" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -843,17 +818,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+          <t>Östra Öknen norra torpet, Vikers sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497053</v>
+        <v>497049</v>
       </c>
       <c r="R3" t="n">
-        <v>6587180</v>
+        <v>6587095</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,29 +874,54 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130333947</v>
+        <v>130333758</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -959,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497041</v>
+        <v>497053</v>
       </c>
       <c r="R4" t="n">
-        <v>6587251</v>
+        <v>6587180</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,9 +987,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,15 +1014,117 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130333947</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Övre Källtorpet, Övre Källtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>497041</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6587251</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Mattias Drejby</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Mattias Drejby</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56959-2025 artfynd.xlsx
+++ b/artfynd/A 56959-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334062</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130003491</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333758</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,8 +1145,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333947</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>